--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/VIRGINIA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/VIRGINIA_2017.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C103">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C227">
@@ -7915,7 +7915,7 @@
         <v>58</v>
       </c>
       <c r="D420">
-        <v>0.009290405253884351</v>
+        <v>0.009290405253884353</v>
       </c>
     </row>
     <row r="421">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C526">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C608">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C609">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C637">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C710">
